--- a/kanban_system/output/library_linked/南方共同市场法规清单.xlsx
+++ b/kanban_system/output/library_linked/南方共同市场法规清单.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="南方共同市场" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="巴西" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阿根廷" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="巴拉圭" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="乌拉圭" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="南方共同市场" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="巴西" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="阿根廷" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="巴拉圭" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="乌拉圭" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="更新" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'南方共同市场'!$A$1:$AC$42</definedName>
